--- a/research/traditional_assets/database/data/bermuda/bermuda_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.189</v>
+        <v>0.137</v>
       </c>
       <c r="E2">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="F2">
         <v>0.1</v>
       </c>
       <c r="G2">
-        <v>0.4932273262661955</v>
+        <v>0.8115208718497615</v>
       </c>
       <c r="H2">
-        <v>0.4932273262661955</v>
+        <v>0.8115208718497615</v>
       </c>
       <c r="I2">
-        <v>0.7468618311924422</v>
+        <v>1.017515498670579</v>
       </c>
       <c r="J2">
-        <v>0.6206288626517978</v>
+        <v>0.8526941545728061</v>
       </c>
       <c r="K2">
-        <v>624.4</v>
+        <v>865</v>
       </c>
       <c r="L2">
-        <v>0.6128778955634079</v>
+        <v>0.8416853167266711</v>
       </c>
       <c r="M2">
-        <v>169.8</v>
+        <v>255.1</v>
       </c>
       <c r="N2">
-        <v>0.03377088305489261</v>
+        <v>0.06091649354060703</v>
       </c>
       <c r="O2">
-        <v>0.2719410634208841</v>
+        <v>0.2949132947976879</v>
       </c>
       <c r="P2">
-        <v>74.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="Q2">
-        <v>0.01489657915672236</v>
+        <v>0.02108556009265229</v>
       </c>
       <c r="R2">
-        <v>0.1199551569506727</v>
+        <v>0.1020809248554913</v>
       </c>
       <c r="S2">
-        <v>94.90000000000001</v>
+        <v>166.8</v>
       </c>
       <c r="T2">
-        <v>0.5588928150765606</v>
+        <v>0.6538612308898472</v>
       </c>
       <c r="U2">
-        <v>65.8</v>
+        <v>79.5</v>
       </c>
       <c r="V2">
-        <v>0.01308671439936356</v>
+        <v>0.01898416792033814</v>
       </c>
       <c r="W2">
-        <v>0.1666622180701988</v>
+        <v>0.2075335892514395</v>
       </c>
       <c r="X2">
-        <v>0.0252111546037962</v>
+        <v>0.05163040771790664</v>
       </c>
       <c r="Y2">
-        <v>0.1414510634664027</v>
+        <v>0.1559031815335329</v>
       </c>
       <c r="Z2">
-        <v>0.2507330377794708</v>
+        <v>0.2318610202125314</v>
       </c>
       <c r="AA2">
-        <v>0.1556121600663032</v>
+        <v>0.1977065366085127</v>
       </c>
       <c r="AB2">
-        <v>0.0258310141725823</v>
+        <v>0.05218920203487645</v>
       </c>
       <c r="AC2">
-        <v>0.1297811458937209</v>
+        <v>0.1455173345736362</v>
       </c>
       <c r="AD2">
-        <v>322.6</v>
+        <v>420.6</v>
       </c>
       <c r="AE2">
-        <v>10.78583190569956</v>
+        <v>7.596610081231695</v>
       </c>
       <c r="AF2">
-        <v>333.3858319056996</v>
+        <v>428.1966100812317</v>
       </c>
       <c r="AG2">
-        <v>267.5858319056996</v>
+        <v>348.6966100812317</v>
       </c>
       <c r="AH2">
-        <v>0.06218277183516895</v>
+        <v>0.09276564148903159</v>
       </c>
       <c r="AI2">
-        <v>0.07406293180706038</v>
+        <v>0.09067358069145026</v>
       </c>
       <c r="AJ2">
-        <v>0.05052997730553347</v>
+        <v>0.07686642947098661</v>
       </c>
       <c r="AK2">
-        <v>0.06032705533075759</v>
+        <v>0.07510324682313591</v>
       </c>
       <c r="AL2">
-        <v>8.34</v>
+        <v>11.7</v>
       </c>
       <c r="AM2">
-        <v>8.34</v>
+        <v>11.7</v>
       </c>
       <c r="AN2">
-        <v>0.4208960676356235</v>
+        <v>0.4004875169012207</v>
       </c>
       <c r="AO2">
-        <v>91.1031175059952</v>
+        <v>89.22222222222223</v>
       </c>
       <c r="AP2">
-        <v>0.3491191085062489</v>
+        <v>0.3320224429940695</v>
       </c>
       <c r="AQ2">
-        <v>91.1031175059952</v>
+        <v>89.22222222222223</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.189</v>
+        <v>0.137</v>
       </c>
       <c r="E3">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="F3">
         <v>0.1</v>
       </c>
       <c r="G3">
-        <v>0.4932273262661955</v>
+        <v>0.8115208718497615</v>
       </c>
       <c r="H3">
-        <v>0.4932273262661955</v>
+        <v>0.8115208718497615</v>
       </c>
       <c r="I3">
-        <v>0.7468618311924422</v>
+        <v>1.017515498670579</v>
       </c>
       <c r="J3">
-        <v>0.6206288626517978</v>
+        <v>0.8526941545728061</v>
       </c>
       <c r="K3">
-        <v>624.4</v>
+        <v>865</v>
       </c>
       <c r="L3">
-        <v>0.6128778955634079</v>
+        <v>0.8416853167266711</v>
       </c>
       <c r="M3">
-        <v>169.8</v>
+        <v>255.1</v>
       </c>
       <c r="N3">
-        <v>0.03377088305489261</v>
+        <v>0.06091649354060703</v>
       </c>
       <c r="O3">
-        <v>0.2719410634208841</v>
+        <v>0.2949132947976879</v>
       </c>
       <c r="P3">
-        <v>74.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="Q3">
-        <v>0.01489657915672236</v>
+        <v>0.02108556009265229</v>
       </c>
       <c r="R3">
-        <v>0.1199551569506727</v>
+        <v>0.1020809248554913</v>
       </c>
       <c r="S3">
-        <v>94.90000000000001</v>
+        <v>166.8</v>
       </c>
       <c r="T3">
-        <v>0.5588928150765606</v>
+        <v>0.6538612308898472</v>
       </c>
       <c r="U3">
-        <v>65.8</v>
+        <v>79.5</v>
       </c>
       <c r="V3">
-        <v>0.01308671439936356</v>
+        <v>0.01898416792033814</v>
       </c>
       <c r="W3">
-        <v>0.1666622180701988</v>
+        <v>0.2075335892514395</v>
       </c>
       <c r="X3">
-        <v>0.0252111546037962</v>
+        <v>0.05163040771790664</v>
       </c>
       <c r="Y3">
-        <v>0.1414510634664027</v>
+        <v>0.1559031815335329</v>
       </c>
       <c r="Z3">
-        <v>0.2507330377794708</v>
+        <v>0.2318610202125314</v>
       </c>
       <c r="AA3">
-        <v>0.1556121600663032</v>
+        <v>0.1977065366085127</v>
       </c>
       <c r="AB3">
-        <v>0.0258310141725823</v>
+        <v>0.05218920203487645</v>
       </c>
       <c r="AC3">
-        <v>0.1297811458937209</v>
+        <v>0.1455173345736362</v>
       </c>
       <c r="AD3">
-        <v>322.6</v>
+        <v>420.6</v>
       </c>
       <c r="AE3">
-        <v>10.78583190569956</v>
+        <v>7.596610081231695</v>
       </c>
       <c r="AF3">
-        <v>333.3858319056996</v>
+        <v>428.1966100812317</v>
       </c>
       <c r="AG3">
-        <v>267.5858319056996</v>
+        <v>348.6966100812317</v>
       </c>
       <c r="AH3">
-        <v>0.06218277183516895</v>
+        <v>0.09276564148903159</v>
       </c>
       <c r="AI3">
-        <v>0.07406293180706038</v>
+        <v>0.09067358069145026</v>
       </c>
       <c r="AJ3">
-        <v>0.05052997730553347</v>
+        <v>0.07686642947098661</v>
       </c>
       <c r="AK3">
-        <v>0.06032705533075759</v>
+        <v>0.07510324682313591</v>
       </c>
       <c r="AL3">
-        <v>8.34</v>
+        <v>11.7</v>
       </c>
       <c r="AM3">
-        <v>8.34</v>
+        <v>11.7</v>
       </c>
       <c r="AN3">
-        <v>0.4208960676356235</v>
+        <v>0.4004875169012207</v>
       </c>
       <c r="AO3">
-        <v>91.1031175059952</v>
+        <v>89.22222222222223</v>
       </c>
       <c r="AP3">
-        <v>0.3491191085062489</v>
+        <v>0.3320224429940695</v>
       </c>
       <c r="AQ3">
-        <v>91.1031175059952</v>
+        <v>89.22222222222223</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.137</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="E2">
-        <v>0.253</v>
+        <v>0.0592</v>
       </c>
       <c r="F2">
         <v>0.1</v>
       </c>
       <c r="G2">
-        <v>0.8115208718497615</v>
+        <v>0.978140483823958</v>
       </c>
       <c r="H2">
-        <v>0.8115208718497615</v>
+        <v>0.978140483823958</v>
       </c>
       <c r="I2">
-        <v>1.017515498670579</v>
+        <v>0.8036985260091092</v>
       </c>
       <c r="J2">
-        <v>0.8526941545728061</v>
+        <v>0.6774175217963286</v>
       </c>
       <c r="K2">
-        <v>865</v>
+        <v>668.4</v>
       </c>
       <c r="L2">
-        <v>0.8416853167266711</v>
+        <v>0.6493733605362868</v>
       </c>
       <c r="M2">
-        <v>255.1</v>
+        <v>160.4</v>
       </c>
       <c r="N2">
-        <v>0.06091649354060703</v>
+        <v>0.02848770091466122</v>
       </c>
       <c r="O2">
-        <v>0.2949132947976879</v>
+        <v>0.2399760622381807</v>
       </c>
       <c r="P2">
-        <v>88.3</v>
+        <v>104.4</v>
       </c>
       <c r="Q2">
-        <v>0.02108556009265229</v>
+        <v>0.01854187017138798</v>
       </c>
       <c r="R2">
-        <v>0.1020809248554913</v>
+        <v>0.1561938958707361</v>
       </c>
       <c r="S2">
-        <v>166.8</v>
+        <v>56</v>
       </c>
       <c r="T2">
-        <v>0.6538612308898472</v>
+        <v>0.3491271820448877</v>
       </c>
       <c r="U2">
-        <v>79.5</v>
+        <v>96.8</v>
       </c>
       <c r="V2">
-        <v>0.01898416792033814</v>
+        <v>0.01719207885622947</v>
       </c>
       <c r="W2">
-        <v>0.2075335892514395</v>
+        <v>0.1556518094173537</v>
       </c>
       <c r="X2">
-        <v>0.05163040771790664</v>
+        <v>0.05386261998272684</v>
       </c>
       <c r="Y2">
-        <v>0.1559031815335329</v>
+        <v>0.1017891894346268</v>
       </c>
       <c r="Z2">
-        <v>0.2318610202125314</v>
+        <v>0.2213993311243014</v>
       </c>
       <c r="AA2">
-        <v>0.1977065366085127</v>
+        <v>0.149979786217589</v>
       </c>
       <c r="AB2">
-        <v>0.05218920203487645</v>
+        <v>0.05389130634681903</v>
       </c>
       <c r="AC2">
-        <v>0.1455173345736362</v>
+        <v>0.09608847987076997</v>
       </c>
       <c r="AD2">
-        <v>420.6</v>
+        <v>421.7</v>
       </c>
       <c r="AE2">
-        <v>7.596610081231695</v>
+        <v>13.76553589411984</v>
       </c>
       <c r="AF2">
-        <v>428.1966100812317</v>
+        <v>435.4655358941199</v>
       </c>
       <c r="AG2">
-        <v>348.6966100812317</v>
+        <v>338.6655358941198</v>
       </c>
       <c r="AH2">
-        <v>0.09276564148903159</v>
+        <v>0.07178833003869556</v>
       </c>
       <c r="AI2">
-        <v>0.09067358069145026</v>
+        <v>0.08304918434442687</v>
       </c>
       <c r="AJ2">
-        <v>0.07686642947098661</v>
+        <v>0.05673582577960643</v>
       </c>
       <c r="AK2">
-        <v>0.07510324682313591</v>
+        <v>0.06580290355613407</v>
       </c>
       <c r="AL2">
-        <v>11.7</v>
+        <v>28.2</v>
       </c>
       <c r="AM2">
-        <v>11.7</v>
+        <v>28.2</v>
       </c>
       <c r="AN2">
-        <v>0.4004875169012207</v>
+        <v>0.505696126633889</v>
       </c>
       <c r="AO2">
-        <v>89.22222222222223</v>
+        <v>29.28014184397163</v>
       </c>
       <c r="AP2">
-        <v>0.3320224429940695</v>
+        <v>0.4061224797866889</v>
       </c>
       <c r="AQ2">
-        <v>89.22222222222223</v>
+        <v>29.28014184397163</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.137</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="E3">
-        <v>0.253</v>
+        <v>0.0592</v>
       </c>
       <c r="F3">
         <v>0.1</v>
       </c>
       <c r="G3">
-        <v>0.8115208718497615</v>
+        <v>0.978140483823958</v>
       </c>
       <c r="H3">
-        <v>0.8115208718497615</v>
+        <v>0.978140483823958</v>
       </c>
       <c r="I3">
-        <v>1.017515498670579</v>
+        <v>0.8036985260091092</v>
       </c>
       <c r="J3">
-        <v>0.8526941545728061</v>
+        <v>0.6774175217963286</v>
       </c>
       <c r="K3">
-        <v>865</v>
+        <v>668.4</v>
       </c>
       <c r="L3">
-        <v>0.8416853167266711</v>
+        <v>0.6493733605362868</v>
       </c>
       <c r="M3">
-        <v>255.1</v>
+        <v>160.4</v>
       </c>
       <c r="N3">
-        <v>0.06091649354060703</v>
+        <v>0.02848770091466122</v>
       </c>
       <c r="O3">
-        <v>0.2949132947976879</v>
+        <v>0.2399760622381807</v>
       </c>
       <c r="P3">
-        <v>88.3</v>
+        <v>104.4</v>
       </c>
       <c r="Q3">
-        <v>0.02108556009265229</v>
+        <v>0.01854187017138798</v>
       </c>
       <c r="R3">
-        <v>0.1020809248554913</v>
+        <v>0.1561938958707361</v>
       </c>
       <c r="S3">
-        <v>166.8</v>
+        <v>56</v>
       </c>
       <c r="T3">
-        <v>0.6538612308898472</v>
+        <v>0.3491271820448877</v>
       </c>
       <c r="U3">
-        <v>79.5</v>
+        <v>96.8</v>
       </c>
       <c r="V3">
-        <v>0.01898416792033814</v>
+        <v>0.01719207885622947</v>
       </c>
       <c r="W3">
-        <v>0.2075335892514395</v>
+        <v>0.1556518094173537</v>
       </c>
       <c r="X3">
-        <v>0.05163040771790664</v>
+        <v>0.05386261998272684</v>
       </c>
       <c r="Y3">
-        <v>0.1559031815335329</v>
+        <v>0.1017891894346268</v>
       </c>
       <c r="Z3">
-        <v>0.2318610202125314</v>
+        <v>0.2213993311243014</v>
       </c>
       <c r="AA3">
-        <v>0.1977065366085127</v>
+        <v>0.149979786217589</v>
       </c>
       <c r="AB3">
-        <v>0.05218920203487645</v>
+        <v>0.05389130634681903</v>
       </c>
       <c r="AC3">
-        <v>0.1455173345736362</v>
+        <v>0.09608847987076997</v>
       </c>
       <c r="AD3">
-        <v>420.6</v>
+        <v>421.7</v>
       </c>
       <c r="AE3">
-        <v>7.596610081231695</v>
+        <v>13.76553589411984</v>
       </c>
       <c r="AF3">
-        <v>428.1966100812317</v>
+        <v>435.4655358941199</v>
       </c>
       <c r="AG3">
-        <v>348.6966100812317</v>
+        <v>338.6655358941198</v>
       </c>
       <c r="AH3">
-        <v>0.09276564148903159</v>
+        <v>0.07178833003869556</v>
       </c>
       <c r="AI3">
-        <v>0.09067358069145026</v>
+        <v>0.08304918434442687</v>
       </c>
       <c r="AJ3">
-        <v>0.07686642947098661</v>
+        <v>0.05673582577960643</v>
       </c>
       <c r="AK3">
-        <v>0.07510324682313591</v>
+        <v>0.06580290355613407</v>
       </c>
       <c r="AL3">
-        <v>11.7</v>
+        <v>28.2</v>
       </c>
       <c r="AM3">
-        <v>11.7</v>
+        <v>28.2</v>
       </c>
       <c r="AN3">
-        <v>0.4004875169012207</v>
+        <v>0.505696126633889</v>
       </c>
       <c r="AO3">
-        <v>89.22222222222223</v>
+        <v>29.28014184397163</v>
       </c>
       <c r="AP3">
-        <v>0.3320224429940695</v>
+        <v>0.4061224797866889</v>
       </c>
       <c r="AQ3">
-        <v>89.22222222222223</v>
+        <v>29.28014184397163</v>
       </c>
     </row>
   </sheetData>
